--- a/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0493 - TRIANGLE.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0493 - TRIANGLE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\H&amp;M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA9E37D-3AB2-414D-9854-E5E59459E52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060EA546-2B85-422C-A4DD-2EE89DA96D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -249,9 +249,6 @@
     <t>EXTRACT:1 MUNITES</t>
   </si>
   <si>
-    <t>OZON %30</t>
-  </si>
-  <si>
     <t>PP REPLESMENT BRUSH</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>MOON WASH   (WET)</t>
+  </si>
+  <si>
+    <t>OZON %20</t>
   </si>
 </sst>
 </file>
@@ -1894,9 +1894,315 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="10" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="10" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1915,328 +2221,22 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="10" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="10" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2534,15 +2534,14 @@
     <sheetNames>
       <sheetName val="ALL SAMPLES"/>
       <sheetName val="Sheet1"/>
+      <sheetName val="DATA"/>
       <sheetName val="CUSTOMER"/>
-      <sheetName val="DATA"/>
       <sheetName val="SABLON"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="2">
         <row r="2">
           <cell r="B2" t="str">
             <v>BILAL</v>
@@ -2590,6 +2589,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
@@ -3657,21 +3657,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="170">
+      <c r="C2" s="208">
         <v>46153</v>
       </c>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="170" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="173" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="175"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="213"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3680,17 +3680,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="208" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="182" t="s">
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="183"/>
+      <c r="I3" s="221"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3701,17 +3701,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="184" t="s">
+      <c r="C4" s="222" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="185"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="188"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="226"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3720,17 +3720,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="189">
+      <c r="C5" s="227">
         <v>512241632</v>
       </c>
-      <c r="D5" s="190"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="193"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="229"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="197"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3739,17 +3739,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="194" t="s">
+      <c r="C6" s="205" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="195"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="192"/>
-      <c r="I6" s="193"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="197"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="197"/>
+      <c r="K6" s="198"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3758,17 +3758,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="194" t="s">
+      <c r="C7" s="205" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="195"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="179"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="192"/>
-      <c r="K7" s="193"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="207"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="197"/>
+      <c r="I7" s="198"/>
+      <c r="J7" s="197"/>
+      <c r="K7" s="198"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3777,15 +3777,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="197"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="199"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="179"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="231"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="217"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="192"/>
-      <c r="K8" s="193"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="198"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3794,17 +3794,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="200">
+      <c r="C9" s="202">
         <v>6</v>
       </c>
-      <c r="D9" s="201"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="178"/>
-      <c r="G9" s="179"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="204"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="192"/>
-      <c r="K9" s="193"/>
+      <c r="J9" s="197"/>
+      <c r="K9" s="198"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3813,15 +3813,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="200"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="202"/>
-      <c r="F10" s="178"/>
-      <c r="G10" s="179"/>
+      <c r="C10" s="202"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="217"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="192"/>
-      <c r="K10" s="193"/>
+      <c r="J10" s="197"/>
+      <c r="K10" s="198"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="203"/>
-      <c r="D11" s="204"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="178"/>
-      <c r="G11" s="179"/>
-      <c r="H11" s="192"/>
-      <c r="I11" s="193"/>
-      <c r="J11" s="192"/>
-      <c r="K11" s="193"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="200"/>
+      <c r="E11" s="201"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="197"/>
+      <c r="I11" s="198"/>
+      <c r="J11" s="197"/>
+      <c r="K11" s="198"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3847,17 +3847,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="206" t="s">
+      <c r="C12" s="194" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="207"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="192"/>
-      <c r="I12" s="193"/>
-      <c r="J12" s="192"/>
-      <c r="K12" s="193"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="196"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="198"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="198"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3866,15 +3866,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="203"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="205"/>
-      <c r="F13" s="180"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="192"/>
-      <c r="I13" s="193"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="193"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="218"/>
+      <c r="G13" s="219"/>
+      <c r="H13" s="197"/>
+      <c r="I13" s="198"/>
+      <c r="J13" s="197"/>
+      <c r="K13" s="198"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -3883,17 +3883,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="211" t="s">
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="212"/>
-      <c r="H14" s="215" t="s">
+      <c r="G14" s="183"/>
+      <c r="H14" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="216"/>
+      <c r="I14" s="187"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
       <c r="L14" s="4"/>
@@ -3911,14 +3911,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="213"/>
-      <c r="G15" s="214"/>
-      <c r="H15" s="213"/>
-      <c r="I15" s="217"/>
-      <c r="J15" s="218" t="s">
+      <c r="F15" s="184"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="184"/>
+      <c r="I15" s="188"/>
+      <c r="J15" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="220" t="s">
+      <c r="K15" s="191" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -3944,12 +3944,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="222" t="s">
+      <c r="H16" s="193" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="222"/>
-      <c r="J16" s="219"/>
-      <c r="K16" s="221"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="192"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="B17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="223" t="s">
+      <c r="C17" s="170" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="224"/>
-      <c r="E17" s="224"/>
-      <c r="F17" s="224"/>
-      <c r="G17" s="224"/>
-      <c r="H17" s="224"/>
-      <c r="I17" s="225"/>
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="171"/>
+      <c r="I17" s="172"/>
       <c r="J17" s="39"/>
       <c r="K17" s="40"/>
       <c r="L17" s="25"/>
@@ -3994,13 +3994,13 @@
       <c r="B19" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="226"/>
-      <c r="D19" s="227"/>
-      <c r="E19" s="227"/>
-      <c r="F19" s="227"/>
-      <c r="G19" s="227"/>
-      <c r="H19" s="227"/>
-      <c r="I19" s="228"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="174"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="175"/>
       <c r="J19" s="46"/>
       <c r="K19" s="47"/>
       <c r="L19" s="25"/>
@@ -4014,8 +4014,8 @@
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
       <c r="G20" s="49"/>
-      <c r="H20" s="229"/>
-      <c r="I20" s="230"/>
+      <c r="H20" s="176"/>
+      <c r="I20" s="177"/>
       <c r="J20" s="39"/>
       <c r="K20" s="40"/>
       <c r="L20" s="25"/>
@@ -4054,10 +4054,10 @@
       <c r="G22" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="231" t="s">
+      <c r="H22" s="178" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="232"/>
+      <c r="I22" s="179"/>
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
       <c r="L22" s="25"/>
@@ -4083,10 +4083,10 @@
       <c r="G23" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="231" t="s">
+      <c r="H23" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="232"/>
+      <c r="I23" s="179"/>
       <c r="J23" s="39"/>
       <c r="K23" s="40"/>
       <c r="L23" s="25"/>
@@ -4104,10 +4104,10 @@
       <c r="G24" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="233" t="s">
+      <c r="H24" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="233"/>
+      <c r="I24" s="168"/>
       <c r="J24" s="39"/>
       <c r="K24" s="40"/>
       <c r="L24" s="25"/>
@@ -4159,10 +4159,10 @@
       <c r="G27" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="234" t="s">
+      <c r="H27" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="234"/>
+      <c r="I27" s="161"/>
       <c r="J27" s="39"/>
       <c r="K27" s="63"/>
       <c r="L27" s="25"/>
@@ -4188,10 +4188,10 @@
       <c r="G28" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H28" s="145" t="s">
+      <c r="H28" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="145"/>
+      <c r="I28" s="169"/>
       <c r="J28" s="65"/>
       <c r="K28" s="66"/>
       <c r="L28" s="25"/>
@@ -4211,8 +4211,8 @@
       <c r="E29" s="48"/>
       <c r="F29" s="40"/>
       <c r="G29" s="62"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="169"/>
       <c r="J29" s="65"/>
       <c r="K29" s="66"/>
       <c r="L29" s="25"/>
@@ -4251,10 +4251,10 @@
       <c r="G31" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="234" t="s">
+      <c r="H31" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="I31" s="234"/>
+      <c r="I31" s="161"/>
       <c r="J31" s="39"/>
       <c r="K31" s="63"/>
       <c r="L31" s="25"/>
@@ -4278,10 +4278,10 @@
       <c r="G32" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H32" s="145" t="s">
+      <c r="H32" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="I32" s="145"/>
+      <c r="I32" s="169"/>
       <c r="J32" s="65"/>
       <c r="K32" s="66"/>
       <c r="L32" s="25"/>
@@ -4320,10 +4320,10 @@
       <c r="G34" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="156" t="s">
+      <c r="H34" s="159" t="s">
         <v>52</v>
       </c>
-      <c r="I34" s="156"/>
+      <c r="I34" s="159"/>
       <c r="J34" s="65"/>
       <c r="K34" s="65"/>
       <c r="L34" s="25"/>
@@ -4343,8 +4343,8 @@
       <c r="E35" s="48"/>
       <c r="F35" s="65"/>
       <c r="G35" s="62"/>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
+      <c r="H35" s="159"/>
+      <c r="I35" s="159"/>
       <c r="J35" s="65"/>
       <c r="K35" s="65"/>
       <c r="L35" s="25"/>
@@ -4354,10 +4354,10 @@
       <c r="A36" s="26"/>
       <c r="B36" s="64"/>
       <c r="C36" s="48"/>
-      <c r="D36" s="164"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="165"/>
-      <c r="G36" s="166"/>
+      <c r="D36" s="233"/>
+      <c r="E36" s="234"/>
+      <c r="F36" s="234"/>
+      <c r="G36" s="235"/>
       <c r="H36" s="77"/>
       <c r="I36" s="78"/>
       <c r="J36" s="65"/>
@@ -4369,12 +4369,12 @@
       <c r="A37" s="26"/>
       <c r="B37" s="73"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="164" t="s">
+      <c r="D37" s="233" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="165"/>
-      <c r="F37" s="165"/>
-      <c r="G37" s="166"/>
+      <c r="E37" s="234"/>
+      <c r="F37" s="234"/>
+      <c r="G37" s="235"/>
       <c r="H37" s="72"/>
       <c r="I37" s="76"/>
       <c r="J37" s="75"/>
@@ -4400,10 +4400,10 @@
       <c r="G38" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="H38" s="152" t="s">
+      <c r="H38" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="I38" s="153"/>
+      <c r="I38" s="158"/>
       <c r="J38" s="80"/>
       <c r="K38" s="80"/>
       <c r="L38" s="25"/>
@@ -4427,10 +4427,10 @@
       <c r="G39" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="H39" s="152" t="s">
+      <c r="H39" s="157" t="s">
         <v>57</v>
       </c>
-      <c r="I39" s="153"/>
+      <c r="I39" s="158"/>
       <c r="J39" s="80"/>
       <c r="K39" s="80"/>
       <c r="L39" s="25"/>
@@ -4467,10 +4467,10 @@
       <c r="G41" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="H41" s="159" t="s">
+      <c r="H41" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="I41" s="159"/>
+      <c r="I41" s="160"/>
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="25"/>
@@ -4490,8 +4490,8 @@
       <c r="E42" s="48"/>
       <c r="F42" s="40"/>
       <c r="G42" s="40"/>
-      <c r="H42" s="145"/>
-      <c r="I42" s="145"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="169"/>
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="25"/>
@@ -4501,12 +4501,12 @@
       <c r="A43" s="26"/>
       <c r="B43" s="64"/>
       <c r="C43" s="48"/>
-      <c r="D43" s="167" t="s">
+      <c r="D43" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="168"/>
-      <c r="F43" s="168"/>
-      <c r="G43" s="169"/>
+      <c r="E43" s="152"/>
+      <c r="F43" s="152"/>
+      <c r="G43" s="153"/>
       <c r="H43" s="89"/>
       <c r="I43" s="90"/>
       <c r="J43" s="40"/>
@@ -4519,15 +4519,15 @@
       <c r="B44" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="240" t="s">
+      <c r="C44" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="240"/>
-      <c r="E44" s="240"/>
-      <c r="F44" s="240"/>
-      <c r="G44" s="240"/>
-      <c r="H44" s="235"/>
-      <c r="I44" s="236"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="163"/>
       <c r="J44" s="92"/>
       <c r="K44" s="92"/>
       <c r="L44" s="25"/>
@@ -4549,10 +4549,10 @@
       <c r="G45" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="H45" s="237" t="s">
+      <c r="H45" s="150" t="s">
         <v>64</v>
       </c>
-      <c r="I45" s="237"/>
+      <c r="I45" s="150"/>
       <c r="J45" s="96"/>
       <c r="K45" s="96"/>
       <c r="L45" s="25"/>
@@ -4572,10 +4572,10 @@
       <c r="G46" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="H46" s="237" t="s">
+      <c r="H46" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="I46" s="237"/>
+      <c r="I46" s="150"/>
       <c r="J46" s="96"/>
       <c r="K46" s="96"/>
       <c r="L46" s="25"/>
@@ -4593,8 +4593,8 @@
       <c r="E47" s="95"/>
       <c r="F47" s="96"/>
       <c r="G47" s="96"/>
-      <c r="H47" s="238"/>
-      <c r="I47" s="239"/>
+      <c r="H47" s="164"/>
+      <c r="I47" s="165"/>
       <c r="J47" s="96"/>
       <c r="K47" s="96"/>
       <c r="L47" s="25"/>
@@ -4603,17 +4603,17 @@
     <row r="48" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A48" s="26"/>
       <c r="B48" s="93" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C48" s="94">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D48" s="97"/>
       <c r="E48" s="95"/>
       <c r="F48" s="96"/>
       <c r="G48" s="96"/>
-      <c r="H48" s="238"/>
-      <c r="I48" s="239"/>
+      <c r="H48" s="164"/>
+      <c r="I48" s="165"/>
       <c r="J48" s="96"/>
       <c r="K48" s="96"/>
       <c r="L48" s="25"/>
@@ -4624,15 +4624,15 @@
       <c r="B49" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="167" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="168"/>
-      <c r="F49" s="168"/>
-      <c r="G49" s="169"/>
-      <c r="H49" s="162"/>
-      <c r="I49" s="163"/>
+      <c r="C49" s="151" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="152"/>
+      <c r="E49" s="152"/>
+      <c r="F49" s="152"/>
+      <c r="G49" s="153"/>
+      <c r="H49" s="166"/>
+      <c r="I49" s="167"/>
       <c r="J49" s="99"/>
       <c r="K49" s="99"/>
       <c r="L49" s="25"/>
@@ -4641,7 +4641,7 @@
     <row r="50" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
       <c r="B50" s="45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C50" s="100"/>
       <c r="D50" s="100"/>
@@ -4652,10 +4652,10 @@
       <c r="G50" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="H50" s="152" t="s">
-        <v>72</v>
-      </c>
-      <c r="I50" s="153"/>
+      <c r="H50" s="157" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="158"/>
       <c r="J50" s="101"/>
       <c r="K50" s="101"/>
       <c r="L50" s="25"/>
@@ -4673,10 +4673,10 @@
       <c r="G51" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="H51" s="152" t="s">
-        <v>73</v>
-      </c>
-      <c r="I51" s="153"/>
+      <c r="H51" s="157" t="s">
+        <v>72</v>
+      </c>
+      <c r="I51" s="158"/>
       <c r="J51" s="101"/>
       <c r="K51" s="101"/>
       <c r="L51" s="25"/>
@@ -4702,12 +4702,12 @@
     <row r="53" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
       <c r="B53" s="98"/>
-      <c r="C53" s="241" t="s">
-        <v>74</v>
-      </c>
-      <c r="D53" s="242"/>
-      <c r="E53" s="242"/>
-      <c r="F53" s="243"/>
+      <c r="C53" s="154" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="155"/>
+      <c r="E53" s="155"/>
+      <c r="F53" s="156"/>
       <c r="G53" s="103"/>
       <c r="H53" s="104"/>
       <c r="I53" s="105"/>
@@ -4719,23 +4719,23 @@
     <row r="54" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A54" s="26"/>
       <c r="B54" s="106" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" s="107">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D54" s="40"/>
       <c r="E54" s="40"/>
       <c r="F54" s="40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="H54" s="234" t="s">
-        <v>74</v>
-      </c>
-      <c r="I54" s="234"/>
+        <v>87</v>
+      </c>
+      <c r="H54" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="161"/>
       <c r="J54" s="39"/>
       <c r="K54" s="40"/>
       <c r="L54" s="25"/>
@@ -4747,14 +4747,16 @@
       <c r="C55" s="40"/>
       <c r="D55" s="40"/>
       <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
+      <c r="F55" s="40">
+        <v>15</v>
+      </c>
       <c r="G55" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="H55" s="145" t="s">
-        <v>89</v>
-      </c>
-      <c r="I55" s="145"/>
+      <c r="I55" s="169"/>
       <c r="J55" s="39"/>
       <c r="K55" s="40"/>
       <c r="L55" s="25"/>
@@ -4768,8 +4770,8 @@
       <c r="E56" s="40"/>
       <c r="F56" s="40"/>
       <c r="G56" s="62"/>
-      <c r="H56" s="154"/>
-      <c r="I56" s="155"/>
+      <c r="H56" s="242"/>
+      <c r="I56" s="243"/>
       <c r="J56" s="39"/>
       <c r="K56" s="40"/>
       <c r="L56" s="25"/>
@@ -4783,8 +4785,8 @@
       <c r="E57" s="48"/>
       <c r="F57" s="65"/>
       <c r="G57" s="65"/>
-      <c r="H57" s="156"/>
-      <c r="I57" s="156"/>
+      <c r="H57" s="159"/>
+      <c r="I57" s="159"/>
       <c r="J57" s="80"/>
       <c r="K57" s="110"/>
       <c r="L57" s="25"/>
@@ -4823,10 +4825,10 @@
       <c r="G59" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="H59" s="157" t="s">
+      <c r="H59" s="244" t="s">
         <v>59</v>
       </c>
-      <c r="I59" s="158"/>
+      <c r="I59" s="245"/>
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="4"/>
@@ -4846,8 +4848,8 @@
       <c r="E60" s="113"/>
       <c r="F60" s="65"/>
       <c r="G60" s="65"/>
-      <c r="H60" s="156"/>
-      <c r="I60" s="156"/>
+      <c r="H60" s="159"/>
+      <c r="I60" s="159"/>
       <c r="J60" s="62"/>
       <c r="K60" s="62"/>
       <c r="L60" s="4"/>
@@ -4871,7 +4873,7 @@
     <row r="62" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A62" s="34"/>
       <c r="B62" s="64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C62" s="48">
         <v>5</v>
@@ -4888,10 +4890,10 @@
       <c r="G62" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="H62" s="159" t="s">
-        <v>76</v>
-      </c>
-      <c r="I62" s="159"/>
+      <c r="H62" s="160" t="s">
+        <v>75</v>
+      </c>
+      <c r="I62" s="160"/>
       <c r="J62" s="40"/>
       <c r="K62" s="40"/>
       <c r="L62" s="4"/>
@@ -4909,10 +4911,10 @@
       <c r="G63" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="H63" s="145" t="s">
-        <v>77</v>
-      </c>
-      <c r="I63" s="145"/>
+      <c r="H63" s="169" t="s">
+        <v>76</v>
+      </c>
+      <c r="I63" s="169"/>
       <c r="J63" s="40"/>
       <c r="K63" s="40"/>
       <c r="L63" s="4"/>
@@ -4932,8 +4934,8 @@
       <c r="E64" s="48"/>
       <c r="F64" s="40"/>
       <c r="G64" s="40"/>
-      <c r="H64" s="145"/>
-      <c r="I64" s="145"/>
+      <c r="H64" s="169"/>
+      <c r="I64" s="169"/>
       <c r="J64" s="40"/>
       <c r="K64" s="40"/>
       <c r="L64" s="4"/>
@@ -4957,7 +4959,7 @@
     <row r="66" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A66" s="34"/>
       <c r="B66" s="119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C66" s="114">
         <v>7</v>
@@ -4974,10 +4976,10 @@
       <c r="G66" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H66" s="160" t="s">
-        <v>79</v>
-      </c>
-      <c r="I66" s="160"/>
+      <c r="H66" s="246" t="s">
+        <v>78</v>
+      </c>
+      <c r="I66" s="246"/>
       <c r="J66" s="62"/>
       <c r="K66" s="62"/>
       <c r="L66" s="4"/>
@@ -4995,10 +4997,10 @@
       <c r="G67" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="H67" s="161" t="s">
-        <v>80</v>
-      </c>
-      <c r="I67" s="161"/>
+      <c r="H67" s="247" t="s">
+        <v>79</v>
+      </c>
+      <c r="I67" s="247"/>
       <c r="J67" s="62"/>
       <c r="K67" s="62"/>
       <c r="L67" s="4"/>
@@ -5018,8 +5020,8 @@
       <c r="E68" s="48"/>
       <c r="F68" s="40"/>
       <c r="G68" s="40"/>
-      <c r="H68" s="146"/>
-      <c r="I68" s="146"/>
+      <c r="H68" s="236"/>
+      <c r="I68" s="236"/>
       <c r="J68" s="40"/>
       <c r="K68" s="40"/>
       <c r="L68" s="4"/>
@@ -5028,13 +5030,13 @@
     <row r="69" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A69" s="34"/>
       <c r="B69" s="98"/>
-      <c r="C69" s="147"/>
-      <c r="D69" s="148"/>
-      <c r="E69" s="148"/>
-      <c r="F69" s="148"/>
-      <c r="G69" s="149"/>
-      <c r="H69" s="162"/>
-      <c r="I69" s="163"/>
+      <c r="C69" s="237"/>
+      <c r="D69" s="238"/>
+      <c r="E69" s="238"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="239"/>
+      <c r="H69" s="166"/>
+      <c r="I69" s="167"/>
       <c r="J69" s="99"/>
       <c r="K69" s="99"/>
       <c r="L69" s="4"/>
@@ -5043,7 +5045,7 @@
     <row r="70" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A70" s="34"/>
       <c r="B70" s="120" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="79">
         <v>2</v>
@@ -5058,12 +5060,12 @@
         <v>2</v>
       </c>
       <c r="G70" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="H70" s="157" t="s">
         <v>82</v>
       </c>
-      <c r="H70" s="152" t="s">
-        <v>83</v>
-      </c>
-      <c r="I70" s="153"/>
+      <c r="I70" s="158"/>
       <c r="J70" s="80"/>
       <c r="K70" s="110"/>
       <c r="L70" s="4"/>
@@ -5077,7 +5079,7 @@
       <c r="E71" s="79"/>
       <c r="F71" s="80"/>
       <c r="G71" s="65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H71" s="121"/>
       <c r="I71" s="122"/>
@@ -5099,7 +5101,7 @@
         <v>38</v>
       </c>
       <c r="H72" s="121" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I72" s="81"/>
       <c r="J72" s="80"/>
@@ -5111,12 +5113,12 @@
       <c r="A73" s="34"/>
       <c r="B73" s="123"/>
       <c r="C73" s="124"/>
-      <c r="D73" s="150"/>
-      <c r="E73" s="150"/>
+      <c r="D73" s="240"/>
+      <c r="E73" s="240"/>
       <c r="F73" s="125"/>
       <c r="G73" s="125"/>
-      <c r="H73" s="246"/>
-      <c r="I73" s="246"/>
+      <c r="H73" s="147"/>
+      <c r="I73" s="147"/>
       <c r="J73" s="125"/>
       <c r="K73" s="125"/>
       <c r="L73" s="4"/>
@@ -5125,7 +5127,7 @@
     <row r="74" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A74" s="34"/>
       <c r="B74" s="126" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C74" s="127">
         <v>2</v>
@@ -5142,10 +5144,10 @@
       <c r="G74" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="H74" s="244" t="s">
-        <v>86</v>
-      </c>
-      <c r="I74" s="244"/>
+      <c r="H74" s="145" t="s">
+        <v>85</v>
+      </c>
+      <c r="I74" s="145"/>
       <c r="J74" s="130"/>
       <c r="K74" s="131"/>
       <c r="L74" s="4"/>
@@ -5154,15 +5156,15 @@
     <row r="75" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A75" s="34"/>
       <c r="B75" s="132" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C75" s="130"/>
       <c r="D75" s="130"/>
       <c r="E75" s="130"/>
       <c r="F75" s="133"/>
       <c r="G75" s="131"/>
-      <c r="H75" s="247"/>
-      <c r="I75" s="247"/>
+      <c r="H75" s="148"/>
+      <c r="I75" s="148"/>
       <c r="J75" s="130"/>
       <c r="K75" s="130"/>
       <c r="L75" s="4"/>
@@ -5191,8 +5193,8 @@
       <c r="E77" s="139"/>
       <c r="F77" s="140"/>
       <c r="G77" s="88"/>
-      <c r="H77" s="244"/>
-      <c r="I77" s="244"/>
+      <c r="H77" s="145"/>
+      <c r="I77" s="145"/>
       <c r="J77" s="65"/>
       <c r="K77" s="62"/>
       <c r="L77" s="36"/>
@@ -5206,8 +5208,8 @@
       <c r="E78" s="142"/>
       <c r="F78" s="143"/>
       <c r="G78" s="62"/>
-      <c r="H78" s="245"/>
-      <c r="I78" s="245"/>
+      <c r="H78" s="146"/>
+      <c r="I78" s="146"/>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
       <c r="L78" s="4"/>
@@ -5221,8 +5223,8 @@
       <c r="E79" s="79"/>
       <c r="F79" s="80"/>
       <c r="G79" s="80"/>
-      <c r="H79" s="151"/>
-      <c r="I79" s="151"/>
+      <c r="H79" s="241"/>
+      <c r="I79" s="241"/>
       <c r="J79" s="144"/>
       <c r="K79" s="144"/>
       <c r="L79" s="4"/>
@@ -5308,61 +5310,27 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="D43:G43"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -5379,31 +5347,65 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="14" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="13" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>